--- a/sports_forms/012_fitness_and_health_survey--sports_forms.xlsx
+++ b/sports_forms/012_fitness_and_health_survey--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'running'}</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Running'}</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'biking'}</t>
+          <t>biking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Biking'}</t>
+          <t>Biking</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'dancing'}</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Dancing'}</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_times_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': '1-2 times a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'3-4_times_a_week'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': '3-4 times a week'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'almost_every_day'}</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Almost every day'}</t>
+          <t>Almost every day</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_30_minutes'}</t>
+          <t>less_than_30_minutes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 30 minutes'}</t>
+          <t>Less than 30 minutes</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': '30-60 minutes'}</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'2-4_hours'}</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': '2-4 hours'}</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_per_month'}</t>
+          <t>1-2_per_month</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': '1-2 per month'}</t>
+          <t>1-2 per month</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'2-4_per_month'}</t>
+          <t>2-4_per_month</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': '2-4 per month'}</t>
+          <t>2-4 per month</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'5_or_more_per_month'}</t>
+          <t>5_or_more_per_month</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': '5 or more per month'}</t>
+          <t>5 or more per month</t>
         </is>
       </c>
     </row>
